--- a/InputData/bldgs/EoBSDwEC/Elast of Bldg Svc Demand wrt E Cost.xlsx
+++ b/InputData/bldgs/EoBSDwEC/Elast of Bldg Svc Demand wrt E Cost.xlsx
@@ -1,35 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\InputData\bldgs\EoBSDwEC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shelley\Dropbox (Energy Innovation)\PC (2)\Documents\GitHub_Repositories\eps-us\InputData\bldgs\EoBSDwEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_694D5200193DDFEAD0C84A92CAC7DAC79B815B94" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8ADD6E-4547-4EEB-BEF0-822A37E766B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="140" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15345" yWindow="-16320" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="EoBSDwEC" sheetId="2" r:id="rId2"/>
+    <sheet name="AEO Assumptions" sheetId="3" r:id="rId2"/>
+    <sheet name="EoBSDwEC" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>EoBSDwEC Elasticity of Building Service Demand wrt Energy Cost</t>
   </si>
@@ -40,27 +33,18 @@
     <t>U.S. Energy Information Administration</t>
   </si>
   <si>
-    <t>Assumptions to the Annual Energy Outlook 2015</t>
-  </si>
-  <si>
     <t>Residential</t>
   </si>
   <si>
     <t>http://www.eia.gov/forecasts/aeo/assumptions/pdf/residential.pdf</t>
   </si>
   <si>
-    <t>Residential Demand Module, Page 29</t>
-  </si>
-  <si>
     <t>Commercial</t>
   </si>
   <si>
     <t>http://www.eia.gov/forecasts/aeo/assumptions/pdf/commercial.pdf</t>
   </si>
   <si>
-    <t>Commercial Demand Module, Page 42</t>
-  </si>
-  <si>
     <t>Notes:</t>
   </si>
   <si>
@@ -70,6 +54,21 @@
     <t>rather than equipment change in the model.</t>
   </si>
   <si>
+    <t>electricity</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>natural gas</t>
+  </si>
+  <si>
+    <t>petroleum diesel</t>
+  </si>
+  <si>
+    <t>heat</t>
+  </si>
+  <si>
     <t>In the EIA source material, Residential elasticities are disaggregated by fuel,</t>
   </si>
   <si>
@@ -82,46 +81,54 @@
     <t>refrigeration with other appliances in our model and so disregard this difference.</t>
   </si>
   <si>
-    <t>use US data</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fuel</t>
-  </si>
-  <si>
     <t>Urban Residential</t>
   </si>
   <si>
     <t>Rural Residential</t>
   </si>
   <si>
-    <t>electricity</t>
-  </si>
-  <si>
-    <t>coal</t>
-  </si>
-  <si>
-    <t>natural gas</t>
-  </si>
-  <si>
-    <t>petroleum diesel</t>
-  </si>
-  <si>
-    <t>heat</t>
-  </si>
-  <si>
     <t>biomass</t>
+  </si>
+  <si>
+    <t>kerosene</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>LPG propane or butane</t>
+  </si>
+  <si>
+    <t>hydrogen</t>
+  </si>
+  <si>
+    <t>Elasticity by Fuel (dimensionless)</t>
+  </si>
+  <si>
+    <t>Assumptions to the Annual Energy Outlook 2022</t>
+  </si>
+  <si>
+    <t>Residential Demand Module, Page 9</t>
+  </si>
+  <si>
+    <t>Residential Demand Module</t>
+  </si>
+  <si>
+    <t>Commercial Demand Module</t>
+  </si>
+  <si>
+    <t>Commercial Demand Module, Page 10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -129,7 +136,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -137,23 +144,8 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -188,7 +180,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -205,6 +199,143 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>180192</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>56784</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80972309-8111-66BD-6A2F-004C02B7BC2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9525" y="209550"/>
+          <a:ext cx="6266667" cy="2923809"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>21462</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>161814</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B337E11D-1EDF-D3C7-1972-42AAF5A0D996}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9525" y="3800475"/>
+          <a:ext cx="6107937" cy="888889"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>53975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>37337</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>50552</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56EFCB07-1318-96ED-A6C6-059F652E193A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28575" y="4578350"/>
+          <a:ext cx="6104762" cy="1984127"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -528,19 +659,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.75" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -548,109 +678,129 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="B7" s="1" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="B8" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="B9" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="B11" s="1" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="B12" s="3" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="B13" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="B24" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{EBAAB2B8-6D29-43EA-933D-85C23BAEEBB6}"/>
+    <hyperlink ref="B12" r:id="rId2" xr:uid="{7E80EFC1-B2EB-4244-B4A6-20E4D9863C03}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B545A04D-0C81-4573-BDE4-77F74558811D}">
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.75" customWidth="1"/>
-    <col min="2" max="3" width="19.875" customWidth="1"/>
-    <col min="4" max="4" width="14.125" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.45">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
+    <row r="1" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>19</v>
@@ -659,12 +809,12 @@
         <v>20</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="14.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>-0.3</v>
@@ -676,9 +826,9 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>-0.15</v>
@@ -690,9 +840,9 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>-0.15</v>
@@ -704,9 +854,9 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>-0.15</v>
@@ -718,9 +868,9 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>-0.15</v>
@@ -732,9 +882,9 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>-0.15</v>
@@ -746,47 +896,94 @@
         <v>-0.25</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>-0.15</v>
+      </c>
+      <c r="C8">
+        <v>-0.15</v>
+      </c>
+      <c r="D8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>-0.15</v>
+      </c>
+      <c r="C9">
+        <v>-0.15</v>
+      </c>
+      <c r="D9">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>-0.15</v>
+      </c>
+      <c r="C10">
+        <v>-0.15</v>
+      </c>
+      <c r="D10">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>-0.15</v>
+      </c>
+      <c r="C11">
+        <v>-0.15</v>
+      </c>
+      <c r="D11">
+        <v>-0.25</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -794,24 +991,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -830,70 +1088,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -995,7 +1206,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1004,14 +1215,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb176f07-3112-4ee9-93fd-ae2cb5f3e433">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6b15a3a4-8173-42d6-9deb-398ec38eca4b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5B25C45-04AB-47C4-81EB-5E8F17105CDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEE14AB6-CA05-4150-959A-53BF64B0538B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6675CEC0-62F2-4D92-96E9-2EB7366A3418}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06CD0F6B-9C8B-423C-949E-AC34C55FC1BF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCE1F08-7091-41D8-B571-6150DD1D4A86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{329C7C8A-CDD0-432C-A70E-8452D2C9FBE5}"/>
 </file>